--- a/Data/SupplementalTable1_popinfo.xlsx
+++ b/Data/SupplementalTable1_popinfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dshizuka2/Documents/GitHub/BARS_phenotypic_integration/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B0C4C090-EE23-564D-99B7-EDA98ACA6B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C2E8C81E-DBD4-5F49-8551-0D0D16A9F4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="560" yWindow="1680" windowWidth="25440" windowHeight="15060" xr2:uid="{25583F6A-A9D1-1B41-B93F-65A9E5F57B3B}"/>
+    <workbookView xWindow="9780" yWindow="2820" windowWidth="25440" windowHeight="14980" xr2:uid="{25583F6A-A9D1-1B41-B93F-65A9E5F57B3B}"/>
   </bookViews>
   <sheets>
     <sheet name="pop_info" sheetId="1" r:id="rId1"/>
@@ -155,6 +155,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -482,7 +485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -597,6 +600,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -642,12 +665,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1027,27 +1055,28 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" style="1" customWidth="1"/>
-    <col min="2" max="5" width="10.83203125" style="1"/>
+    <col min="2" max="3" width="10.83203125" style="2"/>
+    <col min="4" max="5" width="10.83203125" style="1"/>
     <col min="6" max="6" width="29" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1055,10 +1084,10 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>40.552813999999998</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>109.99833</v>
       </c>
       <c r="D2" s="1">
@@ -1075,10 +1104,10 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>43.906216000000001</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>125.314668</v>
       </c>
       <c r="D3" s="1">
@@ -1095,10 +1124,10 @@
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>40.0274</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>-105.25190000000001</v>
       </c>
       <c r="D4" s="1">
@@ -1115,10 +1144,10 @@
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>50.322668999999998</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>-5.0195790000000002</v>
       </c>
       <c r="D5" s="1">
@@ -1135,10 +1164,10 @@
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>49.069200000000002</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>14.7112</v>
       </c>
       <c r="D6" s="1">
@@ -1155,10 +1184,10 @@
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>31.413656</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>31.567402000000001</v>
       </c>
       <c r="D7" s="1">
@@ -1175,10 +1204,10 @@
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>45.761237000000001</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>126.60906300000001</v>
       </c>
       <c r="D8" s="1">
@@ -1195,10 +1224,10 @@
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>32.928199999999997</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>35.540700000000001</v>
       </c>
       <c r="D9" s="1">
@@ -1215,10 +1244,10 @@
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>42.45</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>-76.47</v>
       </c>
       <c r="D10" s="1">
@@ -1235,10 +1264,10 @@
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>39.719985999999999</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>98.509743999999998</v>
       </c>
       <c r="D11" s="1">
@@ -1255,10 +1284,10 @@
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>53.730186000000003</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>77.839710999999994</v>
       </c>
       <c r="D12" s="1">
@@ -1275,10 +1304,10 @@
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>50.45966</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>113.461906</v>
       </c>
       <c r="D13" s="1">
@@ -1295,10 +1324,10 @@
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>31.759609130000001</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>-8.0543918080000001</v>
       </c>
       <c r="D14" s="1">
@@ -1315,10 +1344,10 @@
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>56.724300999999997</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>37.774760999999998</v>
       </c>
       <c r="D15" s="1">
@@ -1335,10 +1364,10 @@
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2">
         <v>51.937939</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>114.97281700000001</v>
       </c>
       <c r="D16" s="1">
@@ -1355,10 +1384,10 @@
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2">
         <v>39.925579999999997</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>119.594752</v>
       </c>
       <c r="D17" s="1">
@@ -1375,10 +1404,10 @@
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <v>47.339176000000002</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>123.978505</v>
       </c>
       <c r="D18" s="1">
@@ -1395,10 +1424,10 @@
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>46.753189999999996</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>23.83464</v>
       </c>
       <c r="D19" s="1">
@@ -1415,10 +1444,10 @@
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>55.547978000000001</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>98.666764000000001</v>
       </c>
       <c r="D20" s="1">
@@ -1435,10 +1464,10 @@
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>54.798431000000001</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>99.440597999999994</v>
       </c>
       <c r="D21" s="1">
@@ -1455,10 +1484,10 @@
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="2">
         <v>46.592950000000002</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="2">
         <v>131.248593</v>
       </c>
       <c r="D22" s="1">
@@ -1475,10 +1504,10 @@
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="2">
         <v>25.041435</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="2">
         <v>121.61274400000001</v>
       </c>
       <c r="D23" s="1">
@@ -1495,10 +1524,10 @@
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="2">
         <v>35.976840000000003</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="2">
         <v>139.135625</v>
       </c>
       <c r="D24" s="1">
@@ -1515,10 +1544,10 @@
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="2">
         <v>36.857709999999997</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="2">
         <v>31.160609999999998</v>
       </c>
       <c r="D25" s="1">
@@ -1535,10 +1564,10 @@
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="2">
         <v>57.575132000000004</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="2">
         <v>62.706240000000001</v>
       </c>
       <c r="D26" s="1">
@@ -1555,10 +1584,10 @@
       <c r="A27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="2">
         <v>52.021259000000001</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="2">
         <v>106.590942</v>
       </c>
       <c r="D27" s="1">
@@ -1575,10 +1604,10 @@
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="2">
         <v>38.887590000000003</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="2">
         <v>100.469511</v>
       </c>
       <c r="D28" s="1">
@@ -1592,26 +1621,27 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="5">
         <v>34.780976000000003</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="5">
         <v>113.65069</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="4">
         <v>16</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="4">
         <v>12</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="4" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>